--- a/Design Files/Adv-OLED-v2.0/BOM/Client_BOM_OLED-v2.0.xlsx
+++ b/Design Files/Adv-OLED-v2.0/BOM/Client_BOM_OLED-v2.0.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\chrisbyrd-esp32iotproduct\Design Files\OLED-v2.0\BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\eSpark-Consultants\chrisbyrd-esp32iotproduct\Design Files\Adv-OLED-v2.0\BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="182" uniqueCount="111">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="84">
   <si>
     <t>Component list</t>
   </si>
@@ -45,78 +45,36 @@
     <t>Capacitor</t>
   </si>
   <si>
-    <t>Diode</t>
-  </si>
-  <si>
     <t>Pogo Connector</t>
   </si>
   <si>
-    <t>Wire To Board Connector</t>
-  </si>
-  <si>
     <t>RGB LED</t>
   </si>
   <si>
-    <t>OLED</t>
-  </si>
-  <si>
     <t>Mosfet</t>
   </si>
   <si>
     <t>Resistor</t>
   </si>
   <si>
-    <t>Solder Bridge</t>
-  </si>
-  <si>
     <t>Designator</t>
   </si>
   <si>
-    <t>C1, C2, C3, C9</t>
-  </si>
-  <si>
     <t>C4, C5, C6, C7</t>
   </si>
   <si>
-    <t>C8</t>
-  </si>
-  <si>
-    <t>C11</t>
-  </si>
-  <si>
-    <t>D1</t>
-  </si>
-  <si>
     <t>J1</t>
   </si>
   <si>
-    <t>J2</t>
-  </si>
-  <si>
     <t>LED1</t>
   </si>
   <si>
-    <t>OLED1</t>
-  </si>
-  <si>
     <t>Q1</t>
   </si>
   <si>
-    <t>R1, R2, R3, R7</t>
-  </si>
-  <si>
     <t>R4</t>
   </si>
   <si>
-    <t>R5</t>
-  </si>
-  <si>
-    <t>R6</t>
-  </si>
-  <si>
-    <t>SB1</t>
-  </si>
-  <si>
     <t>SW1, SW2, SW3</t>
   </si>
   <si>
@@ -129,45 +87,15 @@
     <t>CAP CER 0.1UF 50V X5R 0402</t>
   </si>
   <si>
-    <t>CAP CER 4.7UF 10V X5R 0402</t>
-  </si>
-  <si>
-    <t>CAP CER 2.2UF 25V X5R 0402</t>
-  </si>
-  <si>
-    <t>80V Single 1.2V@100mA 4ns 100mA SOD-523 Switching Diode ROHS</t>
-  </si>
-  <si>
     <t>Pogo Pad 2.5mm 4 Pin</t>
   </si>
   <si>
-    <t>CONN HEADER SMD R/A 11POS 1.25MM</t>
-  </si>
-  <si>
     <t>SMD,3.5x3.5mm Light Emitting Diodes (LED) RoHS</t>
   </si>
   <si>
-    <t>SSD1306 0.96 - OLED Displays Modules ROHS</t>
-  </si>
-  <si>
     <t>50V 220mA 3.5Ω@10V,220mA 225mW 1.6V@1mA N Channel SOT-23 MOSFETs ROHS</t>
   </si>
   <si>
-    <t>RES SMD 10K OHM 0.1% 1/10W 0603</t>
-  </si>
-  <si>
-    <t>RES SMD 4.7K OHM 5% 1/10W 0402</t>
-  </si>
-  <si>
-    <t>RES 0 OHM JUMPER 1/16W 0402</t>
-  </si>
-  <si>
-    <t>±1% 412kΩ 0402 Chip Resistor - Surface Mount ROHS</t>
-  </si>
-  <si>
-    <t>Solder Bridge ON</t>
-  </si>
-  <si>
     <t>3mm 2mm Round Button 50mA Top3.65mm SPST 12V SMD Tactile Switches</t>
   </si>
   <si>
@@ -177,27 +105,15 @@
     <t>Cap-0402</t>
   </si>
   <si>
-    <t>SOD-523</t>
-  </si>
-  <si>
     <t>Pogo 4 Pin</t>
   </si>
   <si>
-    <t>53261-1171</t>
-  </si>
-  <si>
     <t>WS2812B-Mini</t>
   </si>
   <si>
-    <t>N096-2864KSWEG01-H30</t>
-  </si>
-  <si>
     <t>Sot-23</t>
   </si>
   <si>
-    <t>Res-0603</t>
-  </si>
-  <si>
     <t>Res-0402</t>
   </si>
   <si>
@@ -210,33 +126,12 @@
     <t>C1005X5R1H104K050BB</t>
   </si>
   <si>
-    <t>CC0402KRX5R6BB475</t>
-  </si>
-  <si>
-    <t>GRM155R61E225KE11D</t>
-  </si>
-  <si>
-    <t>1SS355WT</t>
-  </si>
-  <si>
     <t>POGO Connector 4 Pin</t>
   </si>
   <si>
     <t>BSS138</t>
   </si>
   <si>
-    <t>RT0603BRD0710KL</t>
-  </si>
-  <si>
-    <t>ERJ-2GEJ472X</t>
-  </si>
-  <si>
-    <t>RC0402FR-070RL</t>
-  </si>
-  <si>
-    <t>FRC0402F4123TS</t>
-  </si>
-  <si>
     <t>TS-1185EC-C-D-B</t>
   </si>
   <si>
@@ -249,30 +144,12 @@
     <t>TDK</t>
   </si>
   <si>
-    <t>Murata</t>
-  </si>
-  <si>
-    <t>CBI</t>
-  </si>
-  <si>
-    <t>Molex</t>
-  </si>
-  <si>
     <t>Worldsemi</t>
   </si>
   <si>
-    <t>Newvisio</t>
-  </si>
-  <si>
     <t>Slkor(SLKORMICRO Elec.)</t>
   </si>
   <si>
-    <t>Panasonic</t>
-  </si>
-  <si>
-    <t>FOJAN</t>
-  </si>
-  <si>
     <t>XKB</t>
   </si>
   <si>
@@ -282,24 +159,9 @@
     <t>0.1uF</t>
   </si>
   <si>
-    <t>4.7uF</t>
-  </si>
-  <si>
-    <t>2.2uf</t>
-  </si>
-  <si>
     <t>10K</t>
   </si>
   <si>
-    <t>4.7K</t>
-  </si>
-  <si>
-    <t>0R</t>
-  </si>
-  <si>
-    <t>412K</t>
-  </si>
-  <si>
     <t>Quantity</t>
   </si>
   <si>
@@ -324,46 +186,101 @@
     <t>Value</t>
   </si>
   <si>
-    <t>Quantity (5 Boards)</t>
-  </si>
-  <si>
-    <t>Links</t>
-  </si>
-  <si>
-    <t>Unit Cost (5 Boards)</t>
-  </si>
-  <si>
-    <t>Total Cost (5 Boards)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Total Component Cost </t>
-  </si>
-  <si>
-    <t>Single Board Cost</t>
-  </si>
-  <si>
     <t>Remarks</t>
   </si>
   <si>
-    <t>Digikey</t>
-  </si>
-  <si>
-    <t>CL05A475KP5NRNC</t>
-  </si>
-  <si>
-    <t>Custom Supplier</t>
+    <t>C9</t>
+  </si>
+  <si>
+    <t>FPC Connector</t>
+  </si>
+  <si>
+    <t>J2, J3</t>
+  </si>
+  <si>
+    <t>Clamshell -25℃~+85℃ 18P Bottom Contact Surface Mount 0.5mm SMD,P=0.5mm FFC/FPC Connectors ROHS</t>
+  </si>
+  <si>
+    <t>F0502-B-18-15T-R</t>
+  </si>
+  <si>
+    <t>XFCN</t>
+  </si>
+  <si>
+    <t>Q2</t>
+  </si>
+  <si>
+    <t>Trans Gp Bjt NPN 25V 1.5A 300MW 3-PIN SOT-23 T/r</t>
+  </si>
+  <si>
+    <t>SOT-23</t>
+  </si>
+  <si>
+    <t>SS8050-G</t>
+  </si>
+  <si>
+    <t>Comchip</t>
+  </si>
+  <si>
+    <t>R1, R2, R3</t>
+  </si>
+  <si>
+    <t>RES SMD 10K OHM 1% 1/20W 0201</t>
+  </si>
+  <si>
+    <t>Res-0201</t>
+  </si>
+  <si>
+    <t>RC0201FR-0710KL</t>
+  </si>
+  <si>
+    <t>RES 1K OHM 1% 1/20W 0201</t>
+  </si>
+  <si>
+    <t>RC0201FR-071KP</t>
+  </si>
+  <si>
+    <t>RC0201FR-071KL</t>
+  </si>
+  <si>
+    <t>R5, R6, R7, R8</t>
+  </si>
+  <si>
+    <t>RES SMD 10 OHM 1% 1/5W 0402</t>
+  </si>
+  <si>
+    <t>CRCW040210R0FKEDHP</t>
+  </si>
+  <si>
+    <t>Vishay Dale</t>
+  </si>
+  <si>
+    <t>1K</t>
+  </si>
+  <si>
+    <t>10R</t>
+  </si>
+  <si>
+    <t>Peripheral</t>
+  </si>
+  <si>
+    <t>0.3mm~0.3mm 18 0.5mm Same Side 5cm P=0.5mm FFC/FPC Connect Cables ROHS</t>
+  </si>
+  <si>
+    <t>JS05A-18P-050-4-8</t>
+  </si>
+  <si>
+    <t xml:space="preserve">JUSHUO </t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <numFmts count="3">
+  <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
-    <numFmt numFmtId="165" formatCode="&quot;$&quot;#,##0.0000"/>
-    <numFmt numFmtId="166" formatCode="&quot;$&quot;#,##0.00"/>
   </numFmts>
-  <fonts count="22" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -498,21 +415,6 @@
       <strike/>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color theme="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="14"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -743,8 +645,34 @@
       <left style="medium">
         <color indexed="64"/>
       </left>
-      <right/>
-      <top style="medium">
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
         <color indexed="64"/>
       </top>
       <bottom style="medium">
@@ -752,40 +680,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
-  <cellStyleXfs count="2">
+  <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="66">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -882,10 +781,6 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="8" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="left" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="10" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -921,6 +816,35 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="19" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -930,53 +854,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="2" borderId="15" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="2" borderId="15" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="165" fontId="17" fillId="2" borderId="16" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="3" borderId="14" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="166" fontId="14" fillId="3" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="18" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="3" borderId="11" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
-      <alignment horizontal="center" vertical="top"/>
-      <protection locked="0"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="20" xfId="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
   </cellXfs>
-  <cellStyles count="2">
-    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
+  <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -1002,13 +884,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>15</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>19942</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>15</xdr:col>
+      <xdr:col>11</xdr:col>
       <xdr:colOff>1905000</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
@@ -1316,7 +1198,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:P27"/>
+  <dimension ref="A1:L23"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
@@ -1327,16 +1209,12 @@
     <col min="7" max="7" width="33.42578125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="21.5703125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.42578125" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="8.7109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9.140625" customWidth="1"/>
-    <col min="14" max="14" width="18.7109375" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="19.28515625" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="29.42578125" customWidth="1"/>
+    <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="29.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -1346,89 +1224,73 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="52"/>
-      <c r="K1" s="52"/>
-      <c r="L1" s="52"/>
-      <c r="M1" s="52"/>
-      <c r="N1" s="52"/>
-      <c r="O1" s="52"/>
-      <c r="P1" s="52"/>
-    </row>
-    <row r="2" spans="1:16" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J1" s="62"/>
+      <c r="K1" s="62"/>
+      <c r="L1" s="62"/>
+    </row>
+    <row r="2" spans="1:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
-      <c r="C2" s="41"/>
+      <c r="C2" s="40"/>
       <c r="D2" s="10" t="s">
         <v>0</v>
       </c>
       <c r="E2" s="10"/>
-      <c r="F2" s="48" t="s">
-        <v>96</v>
+      <c r="F2" s="47" t="s">
+        <v>50</v>
       </c>
       <c r="G2" s="11"/>
       <c r="H2" s="11"/>
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="N2" s="3"/>
-      <c r="O2" s="3"/>
-      <c r="P2" s="38"/>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L2" s="38"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
-      <c r="C3" s="42"/>
+      <c r="C3" s="41"/>
       <c r="D3" s="12" t="s">
         <v>1</v>
       </c>
       <c r="E3" s="12"/>
-      <c r="F3" s="49" t="s">
-        <v>97</v>
+      <c r="F3" s="48" t="s">
+        <v>51</v>
       </c>
       <c r="G3" s="12"/>
       <c r="H3" s="12"/>
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="4"/>
-      <c r="M3" s="4"/>
-      <c r="N3" s="4"/>
-      <c r="O3" s="4"/>
-      <c r="P3" s="53"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L3" s="63"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
-      <c r="C4" s="42"/>
+      <c r="C4" s="41"/>
       <c r="D4" s="12" t="s">
         <v>2</v>
       </c>
       <c r="E4" s="12"/>
-      <c r="F4" s="50" t="s">
-        <v>97</v>
+      <c r="F4" s="49" t="s">
+        <v>51</v>
       </c>
       <c r="G4" s="13"/>
       <c r="H4" s="13"/>
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
-      <c r="L4" s="6"/>
-      <c r="M4" s="5"/>
-      <c r="N4" s="5"/>
-      <c r="O4" s="5"/>
-      <c r="P4" s="54"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L4" s="64"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
-      <c r="C5" s="42"/>
+      <c r="C5" s="41"/>
       <c r="D5" s="12" t="s">
         <v>3</v>
       </c>
       <c r="E5" s="12"/>
-      <c r="F5" s="51" t="s">
+      <c r="F5" s="50" t="s">
         <v>5</v>
       </c>
       <c r="G5" s="14"/>
@@ -1436,16 +1298,12 @@
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
-      <c r="L5" s="5"/>
-      <c r="M5" s="5"/>
-      <c r="N5" s="5"/>
-      <c r="O5" s="5"/>
-      <c r="P5" s="54"/>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L5" s="64"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
-      <c r="C6" s="43"/>
+      <c r="C6" s="42"/>
       <c r="D6" s="15"/>
       <c r="E6" s="15"/>
       <c r="F6" s="16"/>
@@ -1454,16 +1312,12 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="5"/>
-      <c r="M6" s="5"/>
-      <c r="N6" s="5"/>
-      <c r="O6" s="5"/>
-      <c r="P6" s="54"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L6" s="64"/>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
-      <c r="C7" s="44"/>
+      <c r="C7" s="43"/>
       <c r="D7" s="17"/>
       <c r="E7" s="17"/>
       <c r="F7" s="18"/>
@@ -1472,16 +1326,12 @@
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="54"/>
-    </row>
-    <row r="8" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L7" s="64"/>
+    </row>
+    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
-      <c r="C8" s="45"/>
+      <c r="C8" s="44"/>
       <c r="D8" s="27"/>
       <c r="E8" s="27"/>
       <c r="F8" s="28"/>
@@ -1490,13 +1340,9 @@
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="54"/>
-    </row>
-    <row r="9" spans="1:16" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L8" s="64"/>
+    </row>
+    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="29" t="s">
         <v>4</v>
@@ -1505,880 +1351,485 @@
         <v>6</v>
       </c>
       <c r="D9" s="29" t="s">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E9" s="29" t="s">
+        <v>19</v>
+      </c>
+      <c r="F9" s="29" t="s">
+        <v>26</v>
+      </c>
+      <c r="G9" s="29" t="s">
+        <v>32</v>
+      </c>
+      <c r="H9" s="29" t="s">
+        <v>38</v>
+      </c>
+      <c r="I9" s="29" t="s">
+        <v>52</v>
+      </c>
+      <c r="J9" s="30" t="s">
+        <v>54</v>
+      </c>
+      <c r="K9" s="29" t="s">
+        <v>47</v>
+      </c>
+      <c r="L9" s="29" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A10" s="1"/>
+      <c r="B10" s="53">
+        <f t="shared" ref="B10:B20" si="0">ROW(B10) - ROW($B$9)</f>
+        <v>1</v>
+      </c>
+      <c r="C10" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="D10" s="37" t="s">
+        <v>13</v>
+      </c>
+      <c r="E10" s="37" t="s">
+        <v>21</v>
+      </c>
+      <c r="F10" s="37" t="s">
+        <v>27</v>
+      </c>
+      <c r="G10" s="37" t="s">
+        <v>34</v>
+      </c>
+      <c r="H10" s="37" t="s">
+        <v>40</v>
+      </c>
+      <c r="I10" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="J10" s="37" t="s">
+        <v>45</v>
+      </c>
+      <c r="K10" s="37">
+        <v>4</v>
+      </c>
+      <c r="L10" s="36"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A11" s="1"/>
+      <c r="B11" s="51">
+        <f>ROW(B11) - ROW($B$9)</f>
+        <v>2</v>
+      </c>
+      <c r="C11" s="52" t="s">
+        <v>7</v>
+      </c>
+      <c r="D11" s="36" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="36" t="s">
+        <v>20</v>
+      </c>
+      <c r="F11" s="36" t="s">
+        <v>27</v>
+      </c>
+      <c r="G11" s="36" t="s">
         <v>33</v>
       </c>
-      <c r="F9" s="29" t="s">
-        <v>50</v>
-      </c>
-      <c r="G9" s="29" t="s">
-        <v>60</v>
-      </c>
-      <c r="H9" s="29" t="s">
-        <v>98</v>
-      </c>
-      <c r="I9" s="29" t="s">
-        <v>73</v>
-      </c>
-      <c r="J9" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="K9" s="29" t="s">
-        <v>93</v>
-      </c>
-      <c r="L9" s="29" t="s">
-        <v>101</v>
-      </c>
-      <c r="M9" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="N9" s="29" t="s">
-        <v>103</v>
-      </c>
-      <c r="O9" s="29" t="s">
-        <v>104</v>
-      </c>
-      <c r="P9" s="29" t="s">
-        <v>107</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="55">
-        <f>ROW(B10) - ROW($B$9)</f>
+      <c r="H11" s="36" t="s">
+        <v>39</v>
+      </c>
+      <c r="I11" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="J11" s="36" t="s">
+        <v>44</v>
+      </c>
+      <c r="K11" s="36">
         <v>1</v>
       </c>
-      <c r="C10" s="56" t="s">
-        <v>7</v>
-      </c>
-      <c r="D10" s="36" t="s">
-        <v>17</v>
-      </c>
-      <c r="E10" s="36" t="s">
-        <v>34</v>
-      </c>
-      <c r="F10" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="G10" s="36" t="s">
-        <v>61</v>
-      </c>
-      <c r="H10" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="I10" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="J10" s="36" t="s">
-        <v>85</v>
-      </c>
-      <c r="K10" s="36">
-        <v>4</v>
-      </c>
-      <c r="L10" s="36">
-        <f>K10*5</f>
-        <v>20</v>
-      </c>
-      <c r="M10" s="67" t="s">
-        <v>108</v>
-      </c>
-      <c r="N10" s="61">
-        <v>7.3999999999999996E-2</v>
-      </c>
-      <c r="O10" s="61">
-        <f>N10*L10</f>
-        <v>1.48</v>
-      </c>
-      <c r="P10" s="36"/>
-    </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="57">
-        <f t="shared" ref="B11:B25" si="0">ROW(B11) - ROW($B$9)</f>
-        <v>2</v>
-      </c>
-      <c r="C11" s="56" t="s">
-        <v>7</v>
-      </c>
-      <c r="D11" s="37" t="s">
-        <v>18</v>
-      </c>
-      <c r="E11" s="37" t="s">
+      <c r="L11" s="37"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="A12" s="1"/>
+      <c r="B12" s="53">
+        <f t="shared" si="0"/>
+        <v>3</v>
+      </c>
+      <c r="C12" s="52" t="s">
+        <v>8</v>
+      </c>
+      <c r="D12" s="55" t="s">
+        <v>14</v>
+      </c>
+      <c r="E12" s="55" t="s">
+        <v>22</v>
+      </c>
+      <c r="F12" s="55" t="s">
+        <v>28</v>
+      </c>
+      <c r="G12" s="55" t="s">
         <v>35</v>
       </c>
-      <c r="F11" s="37" t="s">
-        <v>51</v>
-      </c>
-      <c r="G11" s="37" t="s">
-        <v>62</v>
-      </c>
-      <c r="H11" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="I11" s="37" t="s">
-        <v>75</v>
-      </c>
-      <c r="J11" s="37" t="s">
-        <v>86</v>
-      </c>
-      <c r="K11" s="37">
-        <v>4</v>
-      </c>
-      <c r="L11" s="37">
-        <f t="shared" ref="L11" si="1">K11*5</f>
-        <v>20</v>
-      </c>
-      <c r="M11" s="67" t="s">
-        <v>108</v>
-      </c>
-      <c r="N11" s="62">
-        <v>7.9000000000000001E-2</v>
-      </c>
-      <c r="O11" s="62">
-        <f t="shared" ref="O11" si="2">N11*L11</f>
-        <v>1.58</v>
-      </c>
-      <c r="P11" s="37"/>
-    </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="55">
-        <f>ROW(B12) - ROW($B$9)</f>
-        <v>3</v>
-      </c>
-      <c r="C12" s="56" t="s">
-        <v>7</v>
-      </c>
-      <c r="D12" s="36" t="s">
-        <v>19</v>
-      </c>
-      <c r="E12" s="36" t="s">
-        <v>36</v>
-      </c>
-      <c r="F12" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="G12" s="60" t="s">
-        <v>63</v>
-      </c>
-      <c r="H12" s="36" t="s">
-        <v>109</v>
-      </c>
-      <c r="I12" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="J12" s="36" t="s">
-        <v>87</v>
-      </c>
-      <c r="K12" s="36">
+      <c r="H12" s="55" t="s">
+        <v>53</v>
+      </c>
+      <c r="I12" s="55" t="s">
+        <v>53</v>
+      </c>
+      <c r="J12" s="55" t="s">
+        <v>53</v>
+      </c>
+      <c r="K12" s="55">
         <v>1</v>
       </c>
-      <c r="L12" s="36">
-        <f>K12*5</f>
-        <v>5</v>
-      </c>
-      <c r="M12" s="67" t="s">
-        <v>108</v>
-      </c>
-      <c r="N12" s="61">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="O12" s="61">
-        <f>N12*L12</f>
-        <v>1.4000000000000001</v>
-      </c>
-      <c r="P12" s="36"/>
-    </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L12" s="36"/>
+    </row>
+    <row r="13" spans="1:12" ht="48" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
-      <c r="B13" s="57">
+      <c r="B13" s="53">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="C13" s="56" t="s">
-        <v>7</v>
+      <c r="C13" s="52" t="s">
+        <v>57</v>
       </c>
       <c r="D13" s="37" t="s">
-        <v>20</v>
+        <v>58</v>
       </c>
       <c r="E13" s="37" t="s">
-        <v>37</v>
+        <v>59</v>
       </c>
       <c r="F13" s="37" t="s">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G13" s="37" t="s">
-        <v>64</v>
+        <v>60</v>
       </c>
       <c r="H13" s="37" t="s">
-        <v>99</v>
+        <v>61</v>
       </c>
       <c r="I13" s="37" t="s">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="J13" s="37" t="s">
-        <v>88</v>
+        <v>53</v>
       </c>
       <c r="K13" s="37">
+        <v>2</v>
+      </c>
+      <c r="L13" s="37"/>
+    </row>
+    <row r="14" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="A14" s="1"/>
+      <c r="B14" s="53">
+        <f t="shared" si="0"/>
+        <v>5</v>
+      </c>
+      <c r="C14" s="52" t="s">
+        <v>9</v>
+      </c>
+      <c r="D14" s="37" t="s">
+        <v>15</v>
+      </c>
+      <c r="E14" s="37" t="s">
+        <v>23</v>
+      </c>
+      <c r="F14" s="37" t="s">
+        <v>48</v>
+      </c>
+      <c r="G14" s="37" t="s">
+        <v>29</v>
+      </c>
+      <c r="H14" s="37" t="s">
+        <v>41</v>
+      </c>
+      <c r="I14" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="J14" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="K14" s="37">
         <v>1</v>
       </c>
-      <c r="L13" s="37">
-        <f t="shared" ref="L13" si="3">K13*5</f>
-        <v>5</v>
-      </c>
-      <c r="M13" s="67" t="s">
-        <v>108</v>
-      </c>
-      <c r="N13" s="62">
-        <v>0.21</v>
-      </c>
-      <c r="O13" s="62">
-        <f t="shared" ref="O13" si="4">N13*L13</f>
-        <v>1.05</v>
-      </c>
-      <c r="P13" s="37"/>
-    </row>
-    <row r="14" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="55">
-        <f>ROW(B14) - ROW($B$9)</f>
-        <v>5</v>
-      </c>
-      <c r="C14" s="58" t="s">
-        <v>8</v>
-      </c>
-      <c r="D14" s="36" t="s">
-        <v>21</v>
-      </c>
-      <c r="E14" s="36" t="s">
-        <v>38</v>
-      </c>
-      <c r="F14" s="36" t="s">
-        <v>52</v>
-      </c>
-      <c r="G14" s="36" t="s">
-        <v>65</v>
-      </c>
-      <c r="H14" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="I14" s="36" t="s">
-        <v>77</v>
-      </c>
-      <c r="J14" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="K14" s="36">
-        <v>1</v>
-      </c>
-      <c r="L14" s="36">
-        <f>K14*5</f>
-        <v>5</v>
-      </c>
-      <c r="M14" s="68" t="s">
-        <v>110</v>
-      </c>
-      <c r="N14" s="61" t="s">
-        <v>99</v>
-      </c>
-      <c r="O14" s="61" t="s">
-        <v>99</v>
-      </c>
-      <c r="P14" s="36"/>
-    </row>
-    <row r="15" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="L14" s="36"/>
+    </row>
+    <row r="15" spans="1:12" ht="36" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
-      <c r="B15" s="57">
+      <c r="B15" s="53">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="C15" s="56" t="s">
-        <v>9</v>
-      </c>
-      <c r="D15" s="59" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="59" t="s">
-        <v>39</v>
-      </c>
-      <c r="F15" s="59" t="s">
-        <v>53</v>
-      </c>
-      <c r="G15" s="59" t="s">
-        <v>66</v>
+      <c r="C15" s="52" t="s">
+        <v>10</v>
+      </c>
+      <c r="D15" s="37" t="s">
+        <v>16</v>
+      </c>
+      <c r="E15" s="37" t="s">
+        <v>24</v>
+      </c>
+      <c r="F15" s="37" t="s">
+        <v>30</v>
+      </c>
+      <c r="G15" s="37" t="s">
+        <v>36</v>
       </c>
       <c r="H15" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="I15" s="59" t="s">
-        <v>99</v>
-      </c>
-      <c r="J15" s="59" t="s">
-        <v>99</v>
-      </c>
-      <c r="K15" s="59">
+        <v>42</v>
+      </c>
+      <c r="I15" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="J15" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="K15" s="37">
         <v>1</v>
       </c>
-      <c r="L15" s="59">
-        <f t="shared" ref="L15" si="5">K15*5</f>
-        <v>5</v>
-      </c>
-      <c r="M15" s="68" t="s">
-        <v>110</v>
-      </c>
-      <c r="N15" s="59" t="s">
-        <v>99</v>
-      </c>
-      <c r="O15" s="59" t="s">
-        <v>99</v>
-      </c>
-      <c r="P15" s="37"/>
-    </row>
-    <row r="16" spans="1:16" ht="25.5" x14ac:dyDescent="0.25">
+      <c r="L15" s="37"/>
+    </row>
+    <row r="16" spans="1:12" ht="24" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
-      <c r="B16" s="55">
+      <c r="B16" s="51">
         <f>ROW(B16) - ROW($B$9)</f>
         <v>7</v>
       </c>
-      <c r="C16" s="58" t="s">
+      <c r="C16" s="52" t="s">
         <v>10</v>
       </c>
       <c r="D16" s="36" t="s">
-        <v>23</v>
+        <v>62</v>
       </c>
       <c r="E16" s="36" t="s">
-        <v>40</v>
+        <v>63</v>
       </c>
       <c r="F16" s="36" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
       <c r="G16" s="36" t="s">
-        <v>54</v>
+        <v>65</v>
       </c>
       <c r="H16" s="36" t="s">
-        <v>99</v>
+        <v>66</v>
       </c>
       <c r="I16" s="36" t="s">
-        <v>78</v>
+        <v>53</v>
       </c>
       <c r="J16" s="36" t="s">
-        <v>99</v>
+        <v>53</v>
       </c>
       <c r="K16" s="36">
         <v>1</v>
       </c>
-      <c r="L16" s="36">
-        <f>K16*5</f>
-        <v>5</v>
-      </c>
-      <c r="M16" s="67" t="s">
-        <v>108</v>
-      </c>
-      <c r="N16" s="61">
-        <v>1.25</v>
-      </c>
-      <c r="O16" s="61">
-        <f>N16*L16</f>
-        <v>6.25</v>
-      </c>
-      <c r="P16" s="36"/>
-    </row>
-    <row r="17" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="L16" s="36"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
-      <c r="B17" s="57">
-        <f t="shared" si="0"/>
+      <c r="B17" s="53">
+        <f t="shared" ref="B17" si="1">ROW(B17) - ROW($B$9)</f>
         <v>8</v>
       </c>
-      <c r="C17" s="56" t="s">
+      <c r="C17" s="52" t="s">
         <v>11</v>
       </c>
       <c r="D17" s="37" t="s">
-        <v>24</v>
+        <v>67</v>
       </c>
       <c r="E17" s="37" t="s">
-        <v>41</v>
+        <v>68</v>
       </c>
       <c r="F17" s="37" t="s">
-        <v>94</v>
+        <v>69</v>
       </c>
       <c r="G17" s="37" t="s">
-        <v>55</v>
+        <v>70</v>
       </c>
       <c r="H17" s="37" t="s">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="I17" s="37" t="s">
-        <v>79</v>
-      </c>
-      <c r="J17" s="37"/>
+        <v>53</v>
+      </c>
+      <c r="J17" s="37" t="s">
+        <v>46</v>
+      </c>
       <c r="K17" s="37">
-        <v>1</v>
-      </c>
-      <c r="L17" s="37">
-        <f t="shared" ref="L17" si="6">K17*5</f>
-        <v>5</v>
-      </c>
-      <c r="M17" s="68" t="s">
-        <v>110</v>
-      </c>
-      <c r="N17" s="61" t="s">
-        <v>99</v>
-      </c>
-      <c r="O17" s="61" t="s">
-        <v>99</v>
-      </c>
-      <c r="P17" s="37"/>
-    </row>
-    <row r="18" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+        <v>3</v>
+      </c>
+      <c r="L17" s="37"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
-      <c r="B18" s="55">
+      <c r="B18" s="51">
         <f>ROW(B18) - ROW($B$9)</f>
         <v>9</v>
       </c>
-      <c r="C18" s="58" t="s">
-        <v>12</v>
+      <c r="C18" s="54" t="s">
+        <v>11</v>
       </c>
       <c r="D18" s="36" t="s">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="E18" s="36" t="s">
-        <v>42</v>
-      </c>
-      <c r="F18" s="37" t="s">
-        <v>94</v>
+        <v>71</v>
+      </c>
+      <c r="F18" s="36" t="s">
+        <v>69</v>
       </c>
       <c r="G18" s="36" t="s">
-        <v>56</v>
+        <v>72</v>
       </c>
       <c r="H18" s="36" t="s">
-        <v>99</v>
+        <v>39</v>
       </c>
       <c r="I18" s="36" t="s">
-        <v>80</v>
-      </c>
-      <c r="J18" s="36"/>
+        <v>73</v>
+      </c>
+      <c r="J18" s="36" t="s">
+        <v>78</v>
+      </c>
       <c r="K18" s="36">
         <v>1</v>
       </c>
-      <c r="L18" s="36">
-        <f>K18*5</f>
-        <v>5</v>
-      </c>
-      <c r="M18" s="68" t="s">
-        <v>110</v>
-      </c>
-      <c r="N18" s="61" t="s">
-        <v>99</v>
-      </c>
-      <c r="O18" s="61" t="s">
-        <v>99</v>
-      </c>
-      <c r="P18" s="36"/>
-    </row>
-    <row r="19" spans="1:16" ht="36" x14ac:dyDescent="0.25">
+      <c r="L18" s="36"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
-      <c r="B19" s="57">
+      <c r="B19" s="53">
+        <f t="shared" ref="B19" si="2">ROW(B19) - ROW($B$9)</f>
+        <v>10</v>
+      </c>
+      <c r="C19" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19" s="37" t="s">
+        <v>74</v>
+      </c>
+      <c r="E19" s="37" t="s">
+        <v>75</v>
+      </c>
+      <c r="F19" s="37" t="s">
+        <v>31</v>
+      </c>
+      <c r="G19" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="H19" s="37" t="s">
+        <v>77</v>
+      </c>
+      <c r="I19" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="J19" s="37" t="s">
+        <v>79</v>
+      </c>
+      <c r="K19" s="37">
+        <v>4</v>
+      </c>
+      <c r="L19" s="37"/>
+    </row>
+    <row r="20" spans="1:12" ht="36" x14ac:dyDescent="0.25">
+      <c r="A20" s="1"/>
+      <c r="B20" s="56">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="C19" s="56" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="37" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" s="37" t="s">
+        <v>11</v>
+      </c>
+      <c r="C20" s="57" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="58" t="s">
+        <v>18</v>
+      </c>
+      <c r="E20" s="58" t="s">
+        <v>25</v>
+      </c>
+      <c r="F20" s="36" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="58" t="s">
+        <v>37</v>
+      </c>
+      <c r="H20" s="58" t="s">
         <v>43</v>
       </c>
-      <c r="F19" s="37" t="s">
-        <v>57</v>
-      </c>
-      <c r="G19" s="37" t="s">
-        <v>67</v>
-      </c>
-      <c r="H19" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="I19" s="37" t="s">
+      <c r="I20" s="58" t="s">
+        <v>53</v>
+      </c>
+      <c r="J20" s="58"/>
+      <c r="K20" s="58">
+        <v>3</v>
+      </c>
+      <c r="L20" s="59"/>
+    </row>
+    <row r="21" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="1"/>
+      <c r="B21" s="53">
+        <v>12</v>
+      </c>
+      <c r="C21" s="52" t="s">
+        <v>80</v>
+      </c>
+      <c r="D21" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="E21" s="37" t="s">
         <v>81</v>
       </c>
-      <c r="J19" s="37"/>
-      <c r="K19" s="37">
-        <v>1</v>
-      </c>
-      <c r="L19" s="37">
-        <f t="shared" ref="L19" si="7">K19*5</f>
-        <v>5</v>
-      </c>
-      <c r="M19" s="68" t="s">
-        <v>110</v>
-      </c>
-      <c r="N19" s="61" t="s">
-        <v>99</v>
-      </c>
-      <c r="O19" s="61" t="s">
-        <v>99</v>
-      </c>
-      <c r="P19" s="37"/>
-    </row>
-    <row r="20" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A20" s="1"/>
-      <c r="B20" s="55">
-        <f>ROW(B20) - ROW($B$9)</f>
-        <v>11</v>
-      </c>
-      <c r="C20" s="58" t="s">
-        <v>14</v>
-      </c>
-      <c r="D20" s="36" t="s">
-        <v>27</v>
-      </c>
-      <c r="E20" s="36" t="s">
-        <v>44</v>
-      </c>
-      <c r="F20" s="36" t="s">
-        <v>58</v>
-      </c>
-      <c r="G20" s="36" t="s">
-        <v>68</v>
-      </c>
-      <c r="H20" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="I20" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="J20" s="36" t="s">
-        <v>89</v>
-      </c>
-      <c r="K20" s="36">
-        <v>4</v>
-      </c>
-      <c r="L20" s="36">
-        <f>K20*5</f>
-        <v>20</v>
-      </c>
-      <c r="M20" s="67" t="s">
-        <v>108</v>
-      </c>
-      <c r="N20" s="61">
-        <v>0.28799999999999998</v>
-      </c>
-      <c r="O20" s="61">
-        <f>N20*L20</f>
-        <v>5.76</v>
-      </c>
-      <c r="P20" s="36"/>
-    </row>
-    <row r="21" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A21" s="1"/>
-      <c r="B21" s="57">
-        <f t="shared" si="0"/>
-        <v>12</v>
-      </c>
-      <c r="C21" s="56" t="s">
-        <v>14</v>
-      </c>
-      <c r="D21" s="37" t="s">
-        <v>28</v>
-      </c>
-      <c r="E21" s="37" t="s">
-        <v>45</v>
-      </c>
-      <c r="F21" s="37" t="s">
-        <v>59</v>
+      <c r="F21" s="36" t="s">
+        <v>53</v>
       </c>
       <c r="G21" s="37" t="s">
-        <v>69</v>
+        <v>82</v>
       </c>
       <c r="H21" s="37" t="s">
-        <v>99</v>
+        <v>83</v>
       </c>
       <c r="I21" s="37" t="s">
-        <v>82</v>
+        <v>53</v>
       </c>
       <c r="J21" s="37" t="s">
-        <v>90</v>
+        <v>53</v>
       </c>
       <c r="K21" s="37">
         <v>1</v>
       </c>
-      <c r="L21" s="37">
-        <f t="shared" ref="L21" si="8">K21*5</f>
-        <v>5</v>
-      </c>
-      <c r="M21" s="67" t="s">
-        <v>108</v>
-      </c>
-      <c r="N21" s="62">
-        <v>0.1</v>
-      </c>
-      <c r="O21" s="62">
-        <f t="shared" ref="O21" si="9">N21*L21</f>
-        <v>0.5</v>
-      </c>
-      <c r="P21" s="37"/>
-    </row>
-    <row r="22" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="L21" s="65"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="1"/>
-      <c r="B22" s="55">
-        <f>ROW(B22) - ROW($B$9)</f>
-        <v>13</v>
-      </c>
-      <c r="C22" s="56" t="s">
-        <v>14</v>
-      </c>
-      <c r="D22" s="36" t="s">
-        <v>29</v>
-      </c>
-      <c r="E22" s="36" t="s">
-        <v>46</v>
-      </c>
-      <c r="F22" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="G22" s="36" t="s">
-        <v>70</v>
-      </c>
-      <c r="H22" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="I22" s="36" t="s">
-        <v>74</v>
-      </c>
-      <c r="J22" s="36" t="s">
-        <v>91</v>
-      </c>
-      <c r="K22" s="36">
-        <v>1</v>
-      </c>
-      <c r="L22" s="36">
-        <f>K22*5</f>
-        <v>5</v>
-      </c>
-      <c r="M22" s="67" t="s">
-        <v>108</v>
-      </c>
-      <c r="N22" s="61">
-        <v>0.1</v>
-      </c>
-      <c r="O22" s="61">
-        <f>N22*L22</f>
-        <v>0.5</v>
-      </c>
-      <c r="P22" s="36"/>
-    </row>
-    <row r="23" spans="1:16" ht="30" x14ac:dyDescent="0.25">
+      <c r="B22" s="31"/>
+      <c r="C22" s="45"/>
+      <c r="D22" s="32"/>
+      <c r="E22" s="33"/>
+      <c r="F22" s="34"/>
+      <c r="G22" s="35"/>
+      <c r="H22" s="34"/>
+      <c r="I22" s="35"/>
+      <c r="J22" s="35"/>
+      <c r="K22" s="35"/>
+      <c r="L22" s="39"/>
+    </row>
+    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="1"/>
-      <c r="B23" s="57">
-        <f t="shared" si="0"/>
-        <v>14</v>
-      </c>
-      <c r="C23" s="56" t="s">
-        <v>14</v>
-      </c>
-      <c r="D23" s="37" t="s">
-        <v>30</v>
-      </c>
-      <c r="E23" s="37" t="s">
-        <v>47</v>
-      </c>
-      <c r="F23" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="G23" s="37" t="s">
-        <v>71</v>
-      </c>
-      <c r="H23" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="I23" s="37" t="s">
-        <v>83</v>
-      </c>
-      <c r="J23" s="37" t="s">
-        <v>92</v>
-      </c>
-      <c r="K23" s="37">
-        <v>1</v>
-      </c>
-      <c r="L23" s="37">
-        <f t="shared" ref="L23" si="10">K23*5</f>
-        <v>5</v>
-      </c>
-      <c r="M23" s="68" t="s">
-        <v>110</v>
-      </c>
-      <c r="N23" s="61" t="s">
-        <v>99</v>
-      </c>
-      <c r="O23" s="61" t="s">
-        <v>99</v>
-      </c>
-      <c r="P23" s="37"/>
-    </row>
-    <row r="24" spans="1:16" ht="30" x14ac:dyDescent="0.25">
-      <c r="A24" s="1"/>
-      <c r="B24" s="55">
-        <f>ROW(B24) - ROW($B$9)</f>
-        <v>15</v>
-      </c>
-      <c r="C24" s="58" t="s">
-        <v>15</v>
-      </c>
-      <c r="D24" s="60" t="s">
-        <v>31</v>
-      </c>
-      <c r="E24" s="60" t="s">
-        <v>48</v>
-      </c>
-      <c r="F24" s="60" t="s">
-        <v>94</v>
-      </c>
-      <c r="G24" s="60" t="s">
-        <v>15</v>
-      </c>
-      <c r="H24" s="36" t="s">
-        <v>99</v>
-      </c>
-      <c r="I24" s="60" t="s">
-        <v>99</v>
-      </c>
-      <c r="J24" s="60" t="s">
-        <v>99</v>
-      </c>
-      <c r="K24" s="60">
-        <v>1</v>
-      </c>
-      <c r="L24" s="60">
-        <f>K24*5</f>
-        <v>5</v>
-      </c>
-      <c r="M24" s="68" t="s">
-        <v>110</v>
-      </c>
-      <c r="N24" s="61" t="s">
-        <v>99</v>
-      </c>
-      <c r="O24" s="61" t="s">
-        <v>99</v>
-      </c>
-      <c r="P24" s="36"/>
-    </row>
-    <row r="25" spans="1:16" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="1"/>
-      <c r="B25" s="57">
-        <f t="shared" si="0"/>
-        <v>16</v>
-      </c>
-      <c r="C25" s="56" t="s">
-        <v>95</v>
-      </c>
-      <c r="D25" s="37" t="s">
-        <v>32</v>
-      </c>
-      <c r="E25" s="37" t="s">
-        <v>49</v>
-      </c>
-      <c r="F25" s="36" t="s">
-        <v>94</v>
-      </c>
-      <c r="G25" s="37" t="s">
-        <v>72</v>
-      </c>
-      <c r="H25" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="I25" s="37" t="s">
-        <v>84</v>
-      </c>
-      <c r="J25" s="37" t="s">
-        <v>99</v>
-      </c>
-      <c r="K25" s="37">
-        <v>3</v>
-      </c>
-      <c r="L25" s="37">
-        <f t="shared" ref="L25" si="11">K25*5</f>
-        <v>15</v>
-      </c>
-      <c r="M25" s="68" t="s">
-        <v>110</v>
-      </c>
-      <c r="N25" s="61" t="s">
-        <v>99</v>
-      </c>
-      <c r="O25" s="61" t="s">
-        <v>99</v>
-      </c>
-      <c r="P25" s="37"/>
-    </row>
-    <row r="26" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="1"/>
-      <c r="B26" s="31"/>
-      <c r="C26" s="46"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="33"/>
-      <c r="F26" s="34"/>
-      <c r="G26" s="35"/>
-      <c r="H26" s="35"/>
-      <c r="I26" s="34"/>
-      <c r="J26" s="35"/>
-      <c r="K26" s="35"/>
-      <c r="L26" s="65" t="s">
-        <v>105</v>
-      </c>
-      <c r="M26" s="66"/>
-      <c r="N26" s="66"/>
-      <c r="O26" s="63">
-        <f>SUM(O10:O25)</f>
-        <v>18.52</v>
-      </c>
-      <c r="P26" s="39"/>
-    </row>
-    <row r="27" spans="1:16" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="1"/>
-      <c r="B27" s="24"/>
-      <c r="C27" s="47"/>
-      <c r="D27" s="8"/>
-      <c r="E27" s="9"/>
-      <c r="F27" s="9"/>
-      <c r="G27" s="9"/>
-      <c r="H27" s="9"/>
-      <c r="I27" s="9"/>
-      <c r="J27" s="9"/>
-      <c r="K27" s="9"/>
-      <c r="L27" s="65" t="s">
-        <v>106</v>
-      </c>
-      <c r="M27" s="66"/>
-      <c r="N27" s="66"/>
-      <c r="O27" s="64">
-        <f>O26/5</f>
-        <v>3.7039999999999997</v>
-      </c>
-      <c r="P27" s="40"/>
+      <c r="B23" s="24"/>
+      <c r="C23" s="46"/>
+      <c r="D23" s="8"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="60"/>
+      <c r="K23" s="60"/>
+      <c r="L23" s="61"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
-    <mergeCell ref="J1:P1"/>
-    <mergeCell ref="P3:P8"/>
-    <mergeCell ref="L26:N26"/>
-    <mergeCell ref="L27:N27"/>
+  <mergeCells count="2">
+    <mergeCell ref="J1:L1"/>
+    <mergeCell ref="L3:L8"/>
   </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="M10" r:id="rId1"/>
-    <hyperlink ref="M11" r:id="rId2"/>
-    <hyperlink ref="M12" r:id="rId3"/>
-    <hyperlink ref="M13" r:id="rId4"/>
-    <hyperlink ref="M16" r:id="rId5"/>
-    <hyperlink ref="M20" r:id="rId6"/>
-    <hyperlink ref="M21" r:id="rId7"/>
-    <hyperlink ref="M22" r:id="rId8"/>
-  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId9"/>
-  <drawing r:id="rId10"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Design Files/Adv-OLED-v2.0/BOM/Client_BOM_OLED-v2.0.xlsx
+++ b/Design Files/Adv-OLED-v2.0/BOM/Client_BOM_OLED-v2.0.xlsx
@@ -12,14 +12,14 @@
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
+    <sheet name="5 Boards" sheetId="1" r:id="rId1"/>
   </sheets>
   <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="114" uniqueCount="84">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="88">
   <si>
     <t>Component list</t>
   </si>
@@ -271,6 +271,18 @@
   </si>
   <si>
     <t xml:space="preserve">JUSHUO </t>
+  </si>
+  <si>
+    <t>Quantity 5 Board</t>
+  </si>
+  <si>
+    <t>2.4-inch tft LCD display SPI serial port color ST7789ILI9341 4IO port can be driven</t>
+  </si>
+  <si>
+    <t>ST7789ILI9341</t>
+  </si>
+  <si>
+    <t>Reference Link</t>
   </si>
 </sst>
 </file>
@@ -280,7 +292,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="[$-409]h:mm:ss\ AM/PM;@"/>
   </numFmts>
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="21" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -415,6 +427,14 @@
       <strike/>
       <sz val="9"/>
       <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -681,10 +701,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="68">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -845,6 +866,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="17" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -854,11 +878,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="2" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="20" fillId="2" borderId="15" xfId="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
+    <cellStyle name="Hyperlink" xfId="1" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
@@ -884,13 +910,13 @@
 <xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>47625</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>19942</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>11</xdr:col>
+      <xdr:col>12</xdr:col>
       <xdr:colOff>1905000</xdr:colOff>
       <xdr:row>7</xdr:row>
       <xdr:rowOff>171450</xdr:rowOff>
@@ -1198,7 +1224,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:M24"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="3.140625" style="25" customWidth="1"/>
@@ -1211,10 +1237,12 @@
     <col min="9" max="9" width="21.42578125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="8.7109375" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="29.42578125" customWidth="1"/>
+    <col min="12" max="12" width="18.28515625" customWidth="1"/>
+    <col min="13" max="13" width="29.42578125" customWidth="1"/>
+    <col min="15" max="15" width="25.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1"/>
       <c r="B1" s="19"/>
       <c r="C1" s="19"/>
@@ -1224,11 +1252,12 @@
       <c r="G1" s="2"/>
       <c r="H1" s="2"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="62"/>
-      <c r="K1" s="62"/>
-      <c r="L1" s="62"/>
-    </row>
-    <row r="2" spans="1:12" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="63"/>
+      <c r="M1" s="63"/>
+    </row>
+    <row r="2" spans="1:13" ht="32.25" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="1"/>
       <c r="B2" s="20"/>
       <c r="C2" s="40"/>
@@ -1244,9 +1273,10 @@
       <c r="I2" s="3"/>
       <c r="J2" s="3"/>
       <c r="K2" s="3"/>
-      <c r="L2" s="38"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L2" s="3"/>
+      <c r="M2" s="38"/>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A3" s="1"/>
       <c r="B3" s="21"/>
       <c r="C3" s="41"/>
@@ -1262,9 +1292,10 @@
       <c r="I3" s="4"/>
       <c r="J3" s="4"/>
       <c r="K3" s="4"/>
-      <c r="L3" s="63"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L3" s="4"/>
+      <c r="M3" s="64"/>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A4" s="1"/>
       <c r="B4" s="21"/>
       <c r="C4" s="41"/>
@@ -1280,9 +1311,10 @@
       <c r="I4" s="6"/>
       <c r="J4" s="6"/>
       <c r="K4" s="6"/>
-      <c r="L4" s="64"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L4" s="66"/>
+      <c r="M4" s="65"/>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A5" s="1"/>
       <c r="B5" s="21"/>
       <c r="C5" s="41"/>
@@ -1298,9 +1330,10 @@
       <c r="I5" s="5"/>
       <c r="J5" s="5"/>
       <c r="K5" s="5"/>
-      <c r="L5" s="64"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L5" s="66"/>
+      <c r="M5" s="65"/>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A6" s="1"/>
       <c r="B6" s="22"/>
       <c r="C6" s="42"/>
@@ -1312,9 +1345,10 @@
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
       <c r="K6" s="5"/>
-      <c r="L6" s="64"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L6" s="66"/>
+      <c r="M6" s="65"/>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A7" s="1"/>
       <c r="B7" s="23"/>
       <c r="C7" s="43"/>
@@ -1326,9 +1360,10 @@
       <c r="I7" s="7"/>
       <c r="J7" s="7"/>
       <c r="K7" s="7"/>
-      <c r="L7" s="64"/>
-    </row>
-    <row r="8" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L7" s="7"/>
+      <c r="M7" s="65"/>
+    </row>
+    <row r="8" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="1"/>
       <c r="B8" s="26"/>
       <c r="C8" s="44"/>
@@ -1340,9 +1375,10 @@
       <c r="I8" s="7"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
-      <c r="L8" s="64"/>
-    </row>
-    <row r="9" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L8" s="7"/>
+      <c r="M8" s="65"/>
+    </row>
+    <row r="9" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="1"/>
       <c r="B9" s="29" t="s">
         <v>4</v>
@@ -1375,10 +1411,13 @@
         <v>47</v>
       </c>
       <c r="L9" s="29" t="s">
+        <v>84</v>
+      </c>
+      <c r="M9" s="29" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A10" s="1"/>
       <c r="B10" s="53">
         <f t="shared" ref="B10:B20" si="0">ROW(B10) - ROW($B$9)</f>
@@ -1411,9 +1450,13 @@
       <c r="K10" s="37">
         <v>4</v>
       </c>
-      <c r="L10" s="36"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L10" s="36">
+        <f>K10*5</f>
+        <v>20</v>
+      </c>
+      <c r="M10" s="36"/>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A11" s="1"/>
       <c r="B11" s="51">
         <f>ROW(B11) - ROW($B$9)</f>
@@ -1446,9 +1489,13 @@
       <c r="K11" s="36">
         <v>1</v>
       </c>
-      <c r="L11" s="37"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L11" s="36">
+        <f t="shared" ref="L11:L22" si="1">K11*5</f>
+        <v>5</v>
+      </c>
+      <c r="M11" s="37"/>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A12" s="1"/>
       <c r="B12" s="53">
         <f t="shared" si="0"/>
@@ -1481,9 +1528,13 @@
       <c r="K12" s="55">
         <v>1</v>
       </c>
-      <c r="L12" s="36"/>
-    </row>
-    <row r="13" spans="1:12" ht="48" x14ac:dyDescent="0.25">
+      <c r="L12" s="36">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="M12" s="36"/>
+    </row>
+    <row r="13" spans="1:13" ht="48" x14ac:dyDescent="0.25">
       <c r="A13" s="1"/>
       <c r="B13" s="53">
         <f t="shared" si="0"/>
@@ -1516,9 +1567,13 @@
       <c r="K13" s="37">
         <v>2</v>
       </c>
-      <c r="L13" s="37"/>
-    </row>
-    <row r="14" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="L13" s="36">
+        <f t="shared" si="1"/>
+        <v>10</v>
+      </c>
+      <c r="M13" s="37"/>
+    </row>
+    <row r="14" spans="1:13" ht="24" x14ac:dyDescent="0.25">
       <c r="A14" s="1"/>
       <c r="B14" s="53">
         <f t="shared" si="0"/>
@@ -1551,9 +1606,13 @@
       <c r="K14" s="37">
         <v>1</v>
       </c>
-      <c r="L14" s="36"/>
-    </row>
-    <row r="15" spans="1:12" ht="36" x14ac:dyDescent="0.25">
+      <c r="L14" s="36">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="M14" s="36"/>
+    </row>
+    <row r="15" spans="1:13" ht="36" x14ac:dyDescent="0.25">
       <c r="A15" s="1"/>
       <c r="B15" s="53">
         <f t="shared" si="0"/>
@@ -1586,9 +1645,13 @@
       <c r="K15" s="37">
         <v>1</v>
       </c>
-      <c r="L15" s="37"/>
-    </row>
-    <row r="16" spans="1:12" ht="24" x14ac:dyDescent="0.25">
+      <c r="L15" s="36">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="M15" s="37"/>
+    </row>
+    <row r="16" spans="1:13" ht="24" x14ac:dyDescent="0.25">
       <c r="A16" s="1"/>
       <c r="B16" s="51">
         <f>ROW(B16) - ROW($B$9)</f>
@@ -1621,12 +1684,16 @@
       <c r="K16" s="36">
         <v>1</v>
       </c>
-      <c r="L16" s="36"/>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L16" s="36">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="M16" s="36"/>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A17" s="1"/>
       <c r="B17" s="53">
-        <f t="shared" ref="B17" si="1">ROW(B17) - ROW($B$9)</f>
+        <f t="shared" ref="B17" si="2">ROW(B17) - ROW($B$9)</f>
         <v>8</v>
       </c>
       <c r="C17" s="52" t="s">
@@ -1656,9 +1723,13 @@
       <c r="K17" s="37">
         <v>3</v>
       </c>
-      <c r="L17" s="37"/>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L17" s="36">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="M17" s="37"/>
+    </row>
+    <row r="18" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A18" s="1"/>
       <c r="B18" s="51">
         <f>ROW(B18) - ROW($B$9)</f>
@@ -1691,12 +1762,16 @@
       <c r="K18" s="36">
         <v>1</v>
       </c>
-      <c r="L18" s="36"/>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L18" s="36">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="M18" s="36"/>
+    </row>
+    <row r="19" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A19" s="1"/>
       <c r="B19" s="53">
-        <f t="shared" ref="B19" si="2">ROW(B19) - ROW($B$9)</f>
+        <f t="shared" ref="B19" si="3">ROW(B19) - ROW($B$9)</f>
         <v>10</v>
       </c>
       <c r="C19" s="54" t="s">
@@ -1726,9 +1801,13 @@
       <c r="K19" s="37">
         <v>4</v>
       </c>
-      <c r="L19" s="37"/>
-    </row>
-    <row r="20" spans="1:12" ht="36" x14ac:dyDescent="0.25">
+      <c r="L19" s="36">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="M19" s="37"/>
+    </row>
+    <row r="20" spans="1:13" ht="36" x14ac:dyDescent="0.25">
       <c r="A20" s="1"/>
       <c r="B20" s="56">
         <f t="shared" si="0"/>
@@ -1759,9 +1838,13 @@
       <c r="K20" s="58">
         <v>3</v>
       </c>
-      <c r="L20" s="59"/>
-    </row>
-    <row r="21" spans="1:12" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="L20" s="36">
+        <f t="shared" si="1"/>
+        <v>15</v>
+      </c>
+      <c r="M20" s="59"/>
+    </row>
+    <row r="21" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="1"/>
       <c r="B21" s="53">
         <v>12</v>
@@ -1793,43 +1876,92 @@
       <c r="K21" s="37">
         <v>1</v>
       </c>
-      <c r="L21" s="65"/>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="L21" s="36">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="M21" s="62"/>
+    </row>
+    <row r="22" spans="1:13" ht="36.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="1"/>
-      <c r="B22" s="31"/>
-      <c r="C22" s="45"/>
-      <c r="D22" s="32"/>
-      <c r="E22" s="33"/>
-      <c r="F22" s="34"/>
-      <c r="G22" s="35"/>
-      <c r="H22" s="34"/>
-      <c r="I22" s="35"/>
-      <c r="J22" s="35"/>
-      <c r="K22" s="35"/>
-      <c r="L22" s="39"/>
-    </row>
-    <row r="23" spans="1:12" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="B22" s="53">
+        <v>12</v>
+      </c>
+      <c r="C22" s="52" t="s">
+        <v>80</v>
+      </c>
+      <c r="D22" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="E22" s="37" t="s">
+        <v>85</v>
+      </c>
+      <c r="F22" s="36" t="s">
+        <v>53</v>
+      </c>
+      <c r="G22" s="37" t="s">
+        <v>86</v>
+      </c>
+      <c r="H22" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="I22" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="J22" s="37" t="s">
+        <v>53</v>
+      </c>
+      <c r="K22" s="37">
+        <v>1</v>
+      </c>
+      <c r="L22" s="36">
+        <f t="shared" si="1"/>
+        <v>5</v>
+      </c>
+      <c r="M22" s="67" t="s">
+        <v>87</v>
+      </c>
+    </row>
+    <row r="23" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A23" s="1"/>
-      <c r="B23" s="24"/>
-      <c r="C23" s="46"/>
-      <c r="D23" s="8"/>
-      <c r="E23" s="9"/>
-      <c r="F23" s="9"/>
-      <c r="G23" s="9"/>
-      <c r="H23" s="9"/>
-      <c r="I23" s="9"/>
-      <c r="J23" s="60"/>
-      <c r="K23" s="60"/>
-      <c r="L23" s="61"/>
+      <c r="B23" s="31"/>
+      <c r="C23" s="45"/>
+      <c r="D23" s="32"/>
+      <c r="E23" s="33"/>
+      <c r="F23" s="34"/>
+      <c r="G23" s="35"/>
+      <c r="H23" s="34"/>
+      <c r="I23" s="35"/>
+      <c r="J23" s="35"/>
+      <c r="K23" s="35"/>
+      <c r="L23" s="35"/>
+      <c r="M23" s="39"/>
+    </row>
+    <row r="24" spans="1:13" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="1"/>
+      <c r="B24" s="24"/>
+      <c r="C24" s="46"/>
+      <c r="D24" s="8"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="60"/>
+      <c r="K24" s="60"/>
+      <c r="L24" s="60"/>
+      <c r="M24" s="61"/>
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="J1:L1"/>
-    <mergeCell ref="L3:L8"/>
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="M3:M8"/>
   </mergeCells>
+  <hyperlinks>
+    <hyperlink ref="M22" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-  <drawing r:id="rId2"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
+  <drawing r:id="rId3"/>
 </worksheet>
 </file>